--- a/Planilhas/Partidas.xlsx
+++ b/Planilhas/Partidas.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junio\OneDrive\Área de Trabalho\Documentos\Scripts Github\automations\Planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_scripts\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA74F7E-D4D4-439C-B64B-2D9901AD6C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D159EF5D-DE30-4223-8D91-03D8D7F3DF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC09E3D1-4513-4E2F-8ACB-59D364663461}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{EC09E3D1-4513-4E2F-8ACB-59D364663461}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>Fornecedor</t>
   </si>
@@ -69,22 +80,37 @@
     <t>Status</t>
   </si>
   <si>
+    <t>COMPENSADO</t>
+  </si>
+  <si>
+    <t>N Reteu GilRat Devido</t>
+  </si>
+  <si>
+    <t>Ajuste Gilrat</t>
+  </si>
+  <si>
     <t>ABERTO</t>
   </si>
   <si>
-    <t>ENTRADA</t>
-  </si>
-  <si>
-    <t>051396430-890</t>
-  </si>
-  <si>
-    <t>Reteu GilRat Indevido</t>
-  </si>
-  <si>
-    <t>Ajuste Gilrat indevido</t>
-  </si>
-  <si>
-    <t>28.04.2026</t>
+    <t>000000137-920</t>
+  </si>
+  <si>
+    <t>N Reteu Funrural e GilRat</t>
+  </si>
+  <si>
+    <t>Ajute Funrural e Gilrat</t>
+  </si>
+  <si>
+    <t>051728063-890</t>
+  </si>
+  <si>
+    <t>02.06.2026</t>
+  </si>
+  <si>
+    <t>10.06.2026</t>
+  </si>
+  <si>
+    <t>DEVOLUÇÃO</t>
   </si>
 </sst>
 </file>
@@ -94,7 +120,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,23 +129,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor theme="5" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -127,96 +171,101 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -229,31 +278,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BDEAC875-DE91-429D-876A-C11EE75EFD35}" name="Tabela1" displayName="Tabela1" ref="A1:L2" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:L2" xr:uid="{BDEAC875-DE91-429D-876A-C11EE75EFD35}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{186AF1EC-45E0-4E99-8A06-498A67BE5007}" name="Fornecedor" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{20895A2B-F978-41A1-A868-F41C4EABC433}" name="Lançamento contábil"/>
-    <tableColumn id="3" xr3:uid="{BB7BCFD4-4B47-4417-AE33-DA0A9DA2211F}" name="Tipo" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{03959FCA-D9C1-4B23-AC62-2A42B66702D2}" name="Valor de crédito/débito" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{17CDAAAE-A882-43D0-AA6B-8A9DE8067D71}" name="Data de vencimento" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{9F6229C2-6E09-448E-A01A-12664739BFC2}" name="Referência" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{47A40145-7219-4C84-8AFC-DFB8C457BDB9}" name="Conta do razão" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{9FC75C98-A207-4029-B977-C326077FDD57}" name="Forma de pagamento" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{308A7DB4-3661-48FA-9DB0-246148A0EEA3}" name="Atribuição" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{27B87367-20D6-480E-ADB6-C4B860C05758}" name="Centro de lucro" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{D6952EAE-05E5-4EF7-A189-4F71A0445BA5}" name="Texto do item" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{49A82F1C-E08F-4E9E-B5B7-8BF2D487E9E2}" name="Status" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -291,7 +319,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -397,7 +425,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -539,112 +567,146 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0565CEC-1E01-4BF4-9FA4-BB54946B0959}">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A196E6-D6A5-4140-B52A-45B0AC06890D}">
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="21.85546875" customWidth="1"/>
-    <col min="9" max="9" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" customWidth="1"/>
-    <col min="11" max="11" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.7109375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1032675</v>
-      </c>
-      <c r="B2" s="7">
-        <v>5800001104</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6">
+        <v>1033107</v>
+      </c>
+      <c r="B2" s="4">
+        <v>5800001848</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="8">
+        <v>168.64</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="7">
+        <v>2101060105</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="6">
+        <v>1033036</v>
+      </c>
+      <c r="B3" s="4">
+        <v>5800001610</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.16</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="7">
+        <v>2101060105</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3">
-        <v>43.74</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="J3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G2">
-        <v>2101060105</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="6" t="s">
+      <c r="L3" s="5" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/Planilhas/Partidas.xlsx
+++ b/Planilhas/Partidas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_scripts\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D159EF5D-DE30-4223-8D91-03D8D7F3DF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BC105B-4981-4C67-AEFC-DE04E2C385D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{EC09E3D1-4513-4E2F-8ACB-59D364663461}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>Fornecedor</t>
   </si>
@@ -83,53 +83,45 @@
     <t>COMPENSADO</t>
   </si>
   <si>
+    <t>Devolução não contabilizada</t>
+  </si>
+  <si>
+    <t>DEVOLUÇÃO</t>
+  </si>
+  <si>
+    <t>ENTRADA</t>
+  </si>
+  <si>
+    <t>051391853-890</t>
+  </si>
+  <si>
     <t>N Reteu GilRat Devido</t>
   </si>
   <si>
     <t>Ajuste Gilrat</t>
   </si>
   <si>
-    <t>ABERTO</t>
-  </si>
-  <si>
-    <t>000000137-920</t>
-  </si>
-  <si>
-    <t>N Reteu Funrural e GilRat</t>
-  </si>
-  <si>
-    <t>Ajute Funrural e Gilrat</t>
-  </si>
-  <si>
-    <t>051728063-890</t>
-  </si>
-  <si>
-    <t>02.06.2026</t>
-  </si>
-  <si>
-    <t>10.06.2026</t>
-  </si>
-  <si>
-    <t>DEVOLUÇÃO</t>
+    <t>051463019-890</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>29.05.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -142,8 +134,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,14 +155,8 @@
         <bgColor theme="5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor theme="5" tint="0.59999389629810485"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -172,98 +165,57 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color theme="0"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color theme="0"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="5">
+    <cellStyle name="Moeda" xfId="4" builtinId="4"/>
+    <cellStyle name="Moeda 2" xfId="3" xr:uid="{8A222096-4313-4048-AD10-A9CED88EFB8C}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Vírgula 2" xfId="1" xr:uid="{ADF5C34D-84F9-4BB1-BC6A-58A60BF8BC20}"/>
+    <cellStyle name="Vírgula 3" xfId="2" xr:uid="{F0624A11-97C8-48B6-A461-1E4C79EF77D9}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -575,134 +527,172 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A196E6-D6A5-4140-B52A-45B0AC06890D}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.08984375" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.6328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.453125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6">
-        <v>1033107</v>
-      </c>
-      <c r="B2" s="4">
-        <v>5800001848</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="8">
-        <v>168.64</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="10" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>1000685</v>
+      </c>
+      <c r="B2" s="3">
+        <v>5100030027</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="10">
+        <v>95.71</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="3">
         <v>2101060105</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>17</v>
+      <c r="L2" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
-        <v>1033036</v>
-      </c>
-      <c r="B3" s="4">
-        <v>5800001610</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0.16</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="A3" s="3">
+        <v>1000685</v>
+      </c>
+      <c r="B3" s="3">
+        <v>5800000820</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="10">
+        <v>220.97</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2101060105</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>1000685</v>
+      </c>
+      <c r="B4" s="3">
+        <v>5800001090</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="10">
+        <v>229.17</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G4" s="3">
         <v>2101060105</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="L4" s="3" t="s">
         <v>14</v>
       </c>
     </row>
